--- a/VerveStacks_KEN_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_KEN_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E52BB76-B605-49EE-9401-3A0A0547BE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7B975BB-78AF-4FA6-A7F6-27F3546BBFBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -924,34 +924,94 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_KEN_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_KEN_013</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_KEN_023</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_solelc_spv_KEN_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
+    <t>distr_solelc_spv_KEN_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_solelc_spv_KEN_004</t>
@@ -960,208 +1020,274 @@
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_solelc_spv_KEN_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_KEN_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_KEN_016</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_solelc_spv_KEN_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_KEN_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_KE14-400_KEN,e_w578140339-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w659874569-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220_KEN,e_r14923640-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220_KEN,e_r14923640-220_KEN,e_w579310367-220_KEN</t>
+  </si>
+  <si>
     <t>e_w563813243-400_KEN</t>
   </si>
   <si>
+    <t>e_w669520367-220_KEN,e_w563813243-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w659874569-220_KEN,e_w669520367-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w86402221-220_KEN,e_w669520367-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w578140339-400_KEN,e_w569997185-400_KEN,e_w457973270-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w669520367-220_KEN,e_w659874569-220_KEN</t>
+  </si>
+  <si>
     <t>e_w669520367-220_KEN</t>
   </si>
   <si>
-    <t>e_w578140339-400_KEN,e_w569997185-400_KEN,e_w457973270-220_KEN</t>
-  </si>
-  <si>
-    <t>e_w669520367-220_KEN,e_w659874569-220_KEN</t>
+    <t>e_KE14-400_KEN,e_w578140339-400_KEN,e_w669520367-220_KEN,e_KE15-220_KEN</t>
   </si>
   <si>
     <t>e_w579310367-220_KEN,e_w563813243-400_KEN</t>
   </si>
   <si>
+    <t>e_w457973270-220_KEN,e_w86402221-220_KEN,e_w669520367-220_KEN</t>
+  </si>
+  <si>
     <t>e_w563813243-400_KEN,e_w669520367-220_KEN</t>
   </si>
   <si>
     <t>e_w1115312336-220_KEN,e_w457973270-220_KEN</t>
   </si>
   <si>
-    <t>e_w457973270-220_KEN,e_w86402221-220_KEN,e_w669520367-220_KEN</t>
-  </si>
-  <si>
-    <t>e_w659874569-220_KEN</t>
-  </si>
-  <si>
-    <t>e_KE14-400_KEN,e_w578140339-400_KEN,e_w669520367-220_KEN,e_KE15-220_KEN</t>
-  </si>
-  <si>
-    <t>e_w86402221-220_KEN,e_w669520367-220_KEN</t>
-  </si>
-  <si>
-    <t>e_KE14-400_KEN,e_w578140339-400_KEN</t>
+    <t>e_w457973270-220_KEN,e_r14923640-220_KEN,e_w579310367-220_KEN,e_w669520367-220_KEN,e_w563813243-400_KEN</t>
+  </si>
+  <si>
+    <t>e_KE15-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE14-400_KEN,e_KE15-220_KEN</t>
   </si>
   <si>
     <t>e_r14923640-220_KEN,e_w579310367-220_KEN,e_w457973270-220_KEN,e_w563813243-400_KEN</t>
   </si>
   <si>
-    <t>e_w1115312336-220_KEN,e_r14923640-220_KEN</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220_KEN,e_r14923640-220_KEN,e_w579310367-220_KEN</t>
-  </si>
-  <si>
-    <t>e_w669520367-220_KEN,e_w563813243-400_KEN</t>
-  </si>
-  <si>
-    <t>e_w659874569-220_KEN,e_w669520367-220_KEN</t>
-  </si>
-  <si>
-    <t>e_KE14-400_KEN,e_KE15-220_KEN</t>
-  </si>
-  <si>
-    <t>e_KE15-220_KEN</t>
-  </si>
-  <si>
-    <t>e_w457973270-220_KEN,e_r14923640-220_KEN,e_w579310367-220_KEN,e_w669520367-220_KEN,e_w563813243-400_KEN</t>
+    <t>distr_wonelc_won_KEN_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_KEN_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
   </si>
   <si>
     <t>distr_wonelc_won_KEN_013</t>
@@ -1176,130 +1302,91 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_KEN_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_KEN_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
+    <t>elc_won_KEN_014</t>
+  </si>
+  <si>
+    <t>e_w457973270-220_KEN,e_w578140339-400_KEN,e_w569997185-400_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_002</t>
+  </si>
+  <si>
+    <t>e_w578140339-400_KEN,e_w669520367-220_KEN,e_KE15-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_019</t>
+  </si>
+  <si>
+    <t>e_w579310367-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_004</t>
+  </si>
+  <si>
+    <t>e_KE15-220_KEN,e_w659874569-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_006</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_017</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_011</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_018</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_022</t>
+  </si>
+  <si>
+    <t>e_w578140339-400_KEN,e_w86402221-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_005</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_007</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_012</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_016</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_021</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_010</t>
+  </si>
+  <si>
+    <t>e_w563813243-400_KEN,e_w669520367-220_KEN,e_w659874569-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_001</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_003</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_020</t>
+  </si>
+  <si>
+    <t>e_w579310367-220_KEN,e_w563813243-400_KEN,e_r14923640-220_KEN</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_009</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_015</t>
+  </si>
+  <si>
+    <t>elc_won_KEN_023</t>
+  </si>
+  <si>
+    <t>e_w578140339-400_KEN</t>
   </si>
   <si>
     <t>elc_won_KEN_013</t>
@@ -1308,91 +1395,52 @@
     <t>elc_won_KEN_008</t>
   </si>
   <si>
-    <t>elc_won_KEN_016</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_021</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_010</t>
-  </si>
-  <si>
-    <t>e_w563813243-400_KEN,e_w669520367-220_KEN,e_w659874569-220_KEN</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_001</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_003</t>
-  </si>
-  <si>
-    <t>e_KE15-220_KEN,e_w659874569-220_KEN</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_012</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_020</t>
-  </si>
-  <si>
-    <t>e_w579310367-220_KEN,e_w563813243-400_KEN,e_r14923640-220_KEN</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_009</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_015</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_023</t>
-  </si>
-  <si>
-    <t>e_w578140339-400_KEN</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_019</t>
-  </si>
-  <si>
-    <t>e_w579310367-220_KEN</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_004</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_007</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_017</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_011</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_006</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_014</t>
-  </si>
-  <si>
-    <t>e_w457973270-220_KEN,e_w578140339-400_KEN,e_w569997185-400_KEN</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_002</t>
-  </si>
-  <si>
-    <t>e_w578140339-400_KEN,e_w669520367-220_KEN,e_KE15-220_KEN</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_018</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_022</t>
-  </si>
-  <si>
-    <t>e_w578140339-400_KEN,e_w86402221-220_KEN</t>
-  </si>
-  <si>
-    <t>elc_won_KEN_005</t>
+    <t>distr_wofelc_wof_KEN_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_KEN_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_KEN_004</t>
@@ -1401,88 +1449,40 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_KEN_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_KEN_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_KEN_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_KEN_006</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_KEN_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_KEN_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_KEN_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_KEN_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_KEN_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
+    <t>elc_wof_KEN_009</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_003</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_007</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_002</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_005</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_008</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_010</t>
+  </si>
+  <si>
+    <t>elc_wof_KEN_001</t>
   </si>
   <si>
     <t>elc_wof_KEN_004</t>
   </si>
   <si>
-    <t>elc_wof_KEN_002</t>
-  </si>
-  <si>
-    <t>elc_wof_KEN_005</t>
-  </si>
-  <si>
-    <t>elc_wof_KEN_009</t>
-  </si>
-  <si>
     <t>elc_wof_KEN_006</t>
-  </si>
-  <si>
-    <t>elc_wof_KEN_001</t>
-  </si>
-  <si>
-    <t>elc_wof_KEN_003</t>
-  </si>
-  <si>
-    <t>elc_wof_KEN_008</t>
-  </si>
-  <si>
-    <t>elc_wof_KEN_010</t>
-  </si>
-  <si>
-    <t>elc_wof_KEN_007</t>
   </si>
   <si>
     <t>e_won_KEN_001</t>
@@ -6505,7 +6505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28A29F4E-E05E-4D65-8B55-779971428BA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB81F02C-A51E-435C-A538-7DABDAE74F54}">
   <dimension ref="B9:BD38"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6743,16 +6743,16 @@
         <v>265</v>
       </c>
       <c r="Y11" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="Z11" t="s">
         <v>325</v>
       </c>
       <c r="AA11">
-        <v>0.98497581152539015</v>
+        <v>0.99515835423076238</v>
       </c>
       <c r="AB11">
-        <v>275.44345536784743</v>
+        <v>88.763505769357138</v>
       </c>
       <c r="AD11" t="s">
         <v>264</v>
@@ -6782,13 +6782,13 @@
         <v>391</v>
       </c>
       <c r="AN11" t="s">
-        <v>325</v>
+        <v>392</v>
       </c>
       <c r="AO11">
-        <v>0.99218690980150615</v>
+        <v>0.9934827767968939</v>
       </c>
       <c r="AP11">
-        <v>143.23998697238727</v>
+        <v>119.4824253902779</v>
       </c>
       <c r="AR11" t="s">
         <v>264</v>
@@ -6818,13 +6818,13 @@
         <v>442</v>
       </c>
       <c r="BB11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="BC11">
-        <v>0.99790507974591136</v>
+        <v>0.99567841910080701</v>
       </c>
       <c r="BD11">
-        <v>38.406871324958367</v>
+        <v>79.228983151871589</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6889,16 +6889,16 @@
         <v>269</v>
       </c>
       <c r="Y12" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="Z12" t="s">
         <v>326</v>
       </c>
       <c r="AA12">
-        <v>0.98549080961480506</v>
+        <v>0.99326495911353319</v>
       </c>
       <c r="AB12">
-        <v>266.00182372857381</v>
+        <v>123.47574958522414</v>
       </c>
       <c r="AD12" t="s">
         <v>264</v>
@@ -6925,16 +6925,16 @@
         <v>347</v>
       </c>
       <c r="AM12" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AN12" t="s">
-        <v>340</v>
+        <v>394</v>
       </c>
       <c r="AO12">
-        <v>0.98910099910393146</v>
+        <v>0.99355139026342754</v>
       </c>
       <c r="AP12">
-        <v>199.81501642792259</v>
+        <v>118.22451183716133</v>
       </c>
       <c r="AR12" t="s">
         <v>264</v>
@@ -6964,13 +6964,13 @@
         <v>443</v>
       </c>
       <c r="BB12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC12">
-        <v>0.99630507039782612</v>
+        <v>0.99722114454285371</v>
       </c>
       <c r="BD12">
-        <v>67.740376039854553</v>
+        <v>50.94568338101594</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7035,16 +7035,16 @@
         <v>271</v>
       </c>
       <c r="Y13" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="Z13" t="s">
         <v>327</v>
       </c>
       <c r="AA13">
-        <v>0.99592595200224132</v>
+        <v>0.9978225971936725</v>
       </c>
       <c r="AB13">
-        <v>74.690879958909605</v>
+        <v>39.919051449338276</v>
       </c>
       <c r="AD13" t="s">
         <v>264</v>
@@ -7071,16 +7071,16 @@
         <v>349</v>
       </c>
       <c r="AM13" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AN13" t="s">
-        <v>325</v>
+        <v>396</v>
       </c>
       <c r="AO13">
-        <v>0.98615336674947807</v>
+        <v>0.99330365963041267</v>
       </c>
       <c r="AP13">
-        <v>253.85494292623497</v>
+        <v>122.76624010910177</v>
       </c>
       <c r="AR13" t="s">
         <v>264</v>
@@ -7110,13 +7110,13 @@
         <v>444</v>
       </c>
       <c r="BB13" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="BC13">
-        <v>0.99749257613418407</v>
+        <v>0.99264898847830307</v>
       </c>
       <c r="BD13">
-        <v>45.969437539958705</v>
+        <v>134.76854456444406</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7181,16 +7181,16 @@
         <v>273</v>
       </c>
       <c r="Y14" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="Z14" t="s">
         <v>328</v>
       </c>
       <c r="AA14">
-        <v>0.99260409516666881</v>
+        <v>0.99787844392938518</v>
       </c>
       <c r="AB14">
-        <v>135.59158861107267</v>
+        <v>38.895194627939205</v>
       </c>
       <c r="AD14" t="s">
         <v>264</v>
@@ -7217,16 +7217,16 @@
         <v>351</v>
       </c>
       <c r="AM14" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AN14" t="s">
-        <v>325</v>
+        <v>398</v>
       </c>
       <c r="AO14">
-        <v>0.99675250681341587</v>
+        <v>0.99458682795119768</v>
       </c>
       <c r="AP14">
-        <v>59.537375087375146</v>
+        <v>99.241487561376104</v>
       </c>
       <c r="AR14" t="s">
         <v>264</v>
@@ -7256,13 +7256,13 @@
         <v>445</v>
       </c>
       <c r="BB14" t="s">
-        <v>399</v>
+        <v>342</v>
       </c>
       <c r="BC14">
-        <v>0.99567841910080701</v>
+        <v>0.99630507039782612</v>
       </c>
       <c r="BD14">
-        <v>79.228983151871589</v>
+        <v>67.740376039854553</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7327,16 +7327,16 @@
         <v>275</v>
       </c>
       <c r="Y15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Z15" t="s">
         <v>329</v>
       </c>
       <c r="AA15">
-        <v>0.99021329006024306</v>
+        <v>0.9893494724125782</v>
       </c>
       <c r="AB15">
-        <v>179.42301556221076</v>
+        <v>195.2596724360663</v>
       </c>
       <c r="AD15" t="s">
         <v>264</v>
@@ -7363,16 +7363,16 @@
         <v>353</v>
       </c>
       <c r="AM15" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AN15" t="s">
-        <v>396</v>
+        <v>334</v>
       </c>
       <c r="AO15">
-        <v>0.97660669020396829</v>
+        <v>0.98563074303391496</v>
       </c>
       <c r="AP15">
-        <v>428.87734626058102</v>
+        <v>263.43637771155954</v>
       </c>
       <c r="AR15" t="s">
         <v>264</v>
@@ -7402,13 +7402,13 @@
         <v>446</v>
       </c>
       <c r="BB15" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="BC15">
-        <v>0.9940284706913598</v>
+        <v>0.99749257613418407</v>
       </c>
       <c r="BD15">
-        <v>109.47803732507046</v>
+        <v>45.969437539958705</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7473,16 +7473,16 @@
         <v>277</v>
       </c>
       <c r="Y16" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="Z16" t="s">
         <v>330</v>
       </c>
       <c r="AA16">
-        <v>0.97548412543178475</v>
+        <v>0.99182980512008645</v>
       </c>
       <c r="AB16">
-        <v>449.45770041728053</v>
+        <v>149.78690613174817</v>
       </c>
       <c r="AD16" t="s">
         <v>264</v>
@@ -7509,16 +7509,16 @@
         <v>355</v>
       </c>
       <c r="AM16" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AN16" t="s">
-        <v>342</v>
+        <v>396</v>
       </c>
       <c r="AO16">
-        <v>0.99172545486986263</v>
+        <v>0.98286027536897036</v>
       </c>
       <c r="AP16">
-        <v>151.6999940525175</v>
+        <v>314.22828490220974</v>
       </c>
       <c r="AR16" t="s">
         <v>264</v>
@@ -7548,13 +7548,13 @@
         <v>447</v>
       </c>
       <c r="BB16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC16">
-        <v>0.99504452373263619</v>
+        <v>0.99417680250918639</v>
       </c>
       <c r="BD16">
-        <v>90.850398235003013</v>
+        <v>106.75862066491723</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7619,16 +7619,16 @@
         <v>279</v>
       </c>
       <c r="Y17" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Z17" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AA17">
-        <v>0.99219647908939179</v>
+        <v>0.97482112792654896</v>
       </c>
       <c r="AB17">
-        <v>143.06455002781746</v>
+        <v>461.61265467993644</v>
       </c>
       <c r="AD17" t="s">
         <v>264</v>
@@ -7655,16 +7655,16 @@
         <v>357</v>
       </c>
       <c r="AM17" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AN17" t="s">
-        <v>399</v>
+        <v>329</v>
       </c>
       <c r="AO17">
-        <v>0.99738740863516284</v>
+        <v>0.98901431127571227</v>
       </c>
       <c r="AP17">
-        <v>47.897508355348883</v>
+        <v>201.40429327860801</v>
       </c>
       <c r="AR17" t="s">
         <v>264</v>
@@ -7694,13 +7694,13 @@
         <v>448</v>
       </c>
       <c r="BB17" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="BC17">
-        <v>0.99722114454285371</v>
+        <v>0.99660062084319445</v>
       </c>
       <c r="BD17">
-        <v>50.94568338101594</v>
+        <v>62.321951208100806</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7765,16 +7765,16 @@
         <v>281</v>
       </c>
       <c r="Y18" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="Z18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AA18">
-        <v>0.99585223303701842</v>
+        <v>0.98069219916089656</v>
       </c>
       <c r="AB18">
-        <v>76.042394321328146</v>
+        <v>353.97634871689564</v>
       </c>
       <c r="AD18" t="s">
         <v>264</v>
@@ -7801,16 +7801,16 @@
         <v>359</v>
       </c>
       <c r="AM18" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN18" t="s">
-        <v>325</v>
+        <v>396</v>
       </c>
       <c r="AO18">
-        <v>0.99486941977940613</v>
+        <v>0.98870306310272893</v>
       </c>
       <c r="AP18">
-        <v>94.060637377553505</v>
+        <v>207.11050978330246</v>
       </c>
       <c r="AR18" t="s">
         <v>264</v>
@@ -7840,13 +7840,13 @@
         <v>449</v>
       </c>
       <c r="BB18" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC18">
-        <v>0.99417680250918639</v>
+        <v>0.99504452373263619</v>
       </c>
       <c r="BD18">
-        <v>106.75862066491723</v>
+        <v>90.850398235003013</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7911,16 +7911,16 @@
         <v>283</v>
       </c>
       <c r="Y19" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="Z19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AA19">
-        <v>0.99686513787774389</v>
+        <v>0.99824425800348515</v>
       </c>
       <c r="AB19">
-        <v>57.472472241362951</v>
+        <v>32.188603269438353</v>
       </c>
       <c r="AD19" t="s">
         <v>264</v>
@@ -7947,16 +7947,16 @@
         <v>361</v>
       </c>
       <c r="AM19" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AN19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AO19">
-        <v>0.99452764457035958</v>
+        <v>0.99495603624977191</v>
       </c>
       <c r="AP19">
-        <v>100.3265162100753</v>
+        <v>92.472668754182365</v>
       </c>
       <c r="AR19" t="s">
         <v>264</v>
@@ -7986,13 +7986,13 @@
         <v>450</v>
       </c>
       <c r="BB19" t="s">
-        <v>333</v>
+        <v>398</v>
       </c>
       <c r="BC19">
-        <v>0.99660062084319445</v>
+        <v>0.99790507974591136</v>
       </c>
       <c r="BD19">
-        <v>62.321951208100806</v>
+        <v>38.406871324958367</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8057,16 +8057,16 @@
         <v>285</v>
       </c>
       <c r="Y20" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="Z20" t="s">
         <v>333</v>
       </c>
       <c r="AA20">
-        <v>0.99022266246501978</v>
+        <v>0.99592595200224132</v>
       </c>
       <c r="AB20">
-        <v>179.25118814130403</v>
+        <v>74.690879958909605</v>
       </c>
       <c r="AD20" t="s">
         <v>264</v>
@@ -8093,16 +8093,16 @@
         <v>363</v>
       </c>
       <c r="AM20" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AN20" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO20">
-        <v>0.97472458044977373</v>
+        <v>0.99059324986934494</v>
       </c>
       <c r="AP20">
-        <v>463.38269175414888</v>
+        <v>172.45708572867548</v>
       </c>
       <c r="AR20" t="s">
         <v>264</v>
@@ -8132,13 +8132,13 @@
         <v>451</v>
       </c>
       <c r="BB20" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="BC20">
-        <v>0.99264898847830307</v>
+        <v>0.9940284706913598</v>
       </c>
       <c r="BD20">
-        <v>134.76854456444406</v>
+        <v>109.47803732507046</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8203,16 +8203,16 @@
         <v>287</v>
       </c>
       <c r="Y21" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z21" t="s">
         <v>334</v>
       </c>
       <c r="AA21">
-        <v>0.99065498411395791</v>
+        <v>0.99260409516666881</v>
       </c>
       <c r="AB21">
-        <v>171.32529124410425</v>
+        <v>135.59158861107267</v>
       </c>
       <c r="AD21" t="s">
         <v>264</v>
@@ -8239,16 +8239,16 @@
         <v>365</v>
       </c>
       <c r="AM21" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AN21" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO21">
-        <v>0.98667278207972509</v>
+        <v>0.98670016097490887</v>
       </c>
       <c r="AP21">
-        <v>244.33232853837262</v>
+        <v>243.83038212667131</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8313,16 +8313,16 @@
         <v>289</v>
       </c>
       <c r="Y22" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="Z22" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="AA22">
-        <v>0.99824425800348515</v>
+        <v>0.98497581152539015</v>
       </c>
       <c r="AB22">
-        <v>32.188603269438353</v>
+        <v>275.44345536784743</v>
       </c>
       <c r="AD22" t="s">
         <v>264</v>
@@ -8349,16 +8349,16 @@
         <v>367</v>
       </c>
       <c r="AM22" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AN22" t="s">
-        <v>406</v>
+        <v>329</v>
       </c>
       <c r="AO22">
-        <v>0.99741412098479176</v>
+        <v>0.99486941977940613</v>
       </c>
       <c r="AP22">
-        <v>47.407781945483563</v>
+        <v>94.060637377553505</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8423,16 +8423,16 @@
         <v>291</v>
       </c>
       <c r="Y23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Z23" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AA23">
-        <v>0.99515835423076238</v>
+        <v>0.98549080961480506</v>
       </c>
       <c r="AB23">
-        <v>88.763505769357138</v>
+        <v>266.00182372857381</v>
       </c>
       <c r="AD23" t="s">
         <v>264</v>
@@ -8459,16 +8459,16 @@
         <v>369</v>
       </c>
       <c r="AM23" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN23" t="s">
-        <v>408</v>
+        <v>329</v>
       </c>
       <c r="AO23">
-        <v>0.99330365963041267</v>
+        <v>0.98615336674947807</v>
       </c>
       <c r="AP23">
-        <v>122.76624010910177</v>
+        <v>253.85494292623497</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8533,16 +8533,16 @@
         <v>293</v>
       </c>
       <c r="Y24" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="Z24" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AA24">
-        <v>0.99326495911353319</v>
+        <v>0.99065498411395791</v>
       </c>
       <c r="AB24">
-        <v>123.47574958522414</v>
+        <v>171.32529124410425</v>
       </c>
       <c r="AD24" t="s">
         <v>264</v>
@@ -8572,13 +8572,13 @@
         <v>409</v>
       </c>
       <c r="AN24" t="s">
-        <v>399</v>
+        <v>329</v>
       </c>
       <c r="AO24">
-        <v>0.99458682795119768</v>
+        <v>0.99675250681341587</v>
       </c>
       <c r="AP24">
-        <v>99.241487561376104</v>
+        <v>59.537375087375146</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8643,16 +8643,16 @@
         <v>295</v>
       </c>
       <c r="Y25" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="Z25" t="s">
         <v>337</v>
       </c>
       <c r="AA25">
-        <v>0.99592997806909844</v>
+        <v>0.99021329006024306</v>
       </c>
       <c r="AB25">
-        <v>74.617068733196106</v>
+        <v>179.42301556221076</v>
       </c>
       <c r="AD25" t="s">
         <v>264</v>
@@ -8682,13 +8682,13 @@
         <v>410</v>
       </c>
       <c r="AN25" t="s">
-        <v>340</v>
+        <v>411</v>
       </c>
       <c r="AO25">
-        <v>0.98670016097490887</v>
+        <v>0.97660669020396829</v>
       </c>
       <c r="AP25">
-        <v>243.83038212667131</v>
+        <v>428.87734626058102</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8753,16 +8753,16 @@
         <v>297</v>
       </c>
       <c r="Y26" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="Z26" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="AA26">
-        <v>0.98440782007749728</v>
+        <v>0.99585223303701842</v>
       </c>
       <c r="AB26">
-        <v>285.85663191255094</v>
+        <v>76.042394321328146</v>
       </c>
       <c r="AD26" t="s">
         <v>264</v>
@@ -8789,16 +8789,16 @@
         <v>375</v>
       </c>
       <c r="AM26" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN26" t="s">
-        <v>408</v>
+        <v>343</v>
       </c>
       <c r="AO26">
-        <v>0.98286027536897036</v>
+        <v>0.99172545486986263</v>
       </c>
       <c r="AP26">
-        <v>314.22828490220974</v>
+        <v>151.6999940525175</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8863,16 +8863,16 @@
         <v>299</v>
       </c>
       <c r="Y27" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="Z27" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="AA27">
-        <v>0.9978225971936725</v>
+        <v>0.99686513787774389</v>
       </c>
       <c r="AB27">
-        <v>39.919051449338276</v>
+        <v>57.472472241362951</v>
       </c>
       <c r="AD27" t="s">
         <v>264</v>
@@ -8899,16 +8899,16 @@
         <v>377</v>
       </c>
       <c r="AM27" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN27" t="s">
-        <v>325</v>
+        <v>398</v>
       </c>
       <c r="AO27">
-        <v>0.98901431127571227</v>
+        <v>0.99738740863516284</v>
       </c>
       <c r="AP27">
-        <v>201.40429327860801</v>
+        <v>47.897508355348883</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8973,16 +8973,16 @@
         <v>301</v>
       </c>
       <c r="Y28" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="Z28" t="s">
         <v>339</v>
       </c>
       <c r="AA28">
-        <v>0.99787844392938518</v>
+        <v>0.99199432528561049</v>
       </c>
       <c r="AB28">
-        <v>38.895194627939205</v>
+        <v>146.77070309714048</v>
       </c>
       <c r="AD28" t="s">
         <v>264</v>
@@ -9009,16 +9009,16 @@
         <v>379</v>
       </c>
       <c r="AM28" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN28" t="s">
-        <v>328</v>
+        <v>415</v>
       </c>
       <c r="AO28">
-        <v>0.98563074303391496</v>
+        <v>0.99452764457035958</v>
       </c>
       <c r="AP28">
-        <v>263.43637771155954</v>
+        <v>100.3265162100753</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9083,16 +9083,16 @@
         <v>303</v>
       </c>
       <c r="Y29" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="Z29" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="AA29">
-        <v>0.9893494724125782</v>
+        <v>0.99219647908939179</v>
       </c>
       <c r="AB29">
-        <v>195.2596724360663</v>
+        <v>143.06455002781746</v>
       </c>
       <c r="AD29" t="s">
         <v>264</v>
@@ -9119,16 +9119,16 @@
         <v>381</v>
       </c>
       <c r="AM29" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN29" t="s">
-        <v>415</v>
+        <v>329</v>
       </c>
       <c r="AO29">
-        <v>0.9934827767968939</v>
+        <v>0.97472458044977373</v>
       </c>
       <c r="AP29">
-        <v>119.4824253902779</v>
+        <v>463.38269175414888</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9193,16 +9193,16 @@
         <v>305</v>
       </c>
       <c r="Y30" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="Z30" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA30">
-        <v>0.99182980512008645</v>
+        <v>0.99117807442989492</v>
       </c>
       <c r="AB30">
-        <v>149.78690613174817</v>
+        <v>161.73530211859338</v>
       </c>
       <c r="AD30" t="s">
         <v>264</v>
@@ -9229,16 +9229,16 @@
         <v>383</v>
       </c>
       <c r="AM30" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN30" t="s">
-        <v>417</v>
+        <v>337</v>
       </c>
       <c r="AO30">
-        <v>0.99355139026342754</v>
+        <v>0.98667278207972509</v>
       </c>
       <c r="AP30">
-        <v>118.22451183716133</v>
+        <v>244.33232853837262</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9303,16 +9303,16 @@
         <v>307</v>
       </c>
       <c r="Y31" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Z31" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="AA31">
-        <v>0.97482112792654896</v>
+        <v>0.99806574344338672</v>
       </c>
       <c r="AB31">
-        <v>461.61265467993644</v>
+        <v>35.461370204576532</v>
       </c>
       <c r="AD31" t="s">
         <v>264</v>
@@ -9342,13 +9342,13 @@
         <v>418</v>
       </c>
       <c r="AN31" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="AO31">
-        <v>0.98870306310272893</v>
+        <v>0.99741412098479176</v>
       </c>
       <c r="AP31">
-        <v>207.11050978330246</v>
+        <v>47.407781945483563</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9413,16 +9413,16 @@
         <v>309</v>
       </c>
       <c r="Y32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z32" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="AA32">
-        <v>0.98069219916089656</v>
+        <v>0.99312290929392577</v>
       </c>
       <c r="AB32">
-        <v>353.97634871689564</v>
+        <v>126.07999627802737</v>
       </c>
       <c r="AD32" t="s">
         <v>264</v>
@@ -9449,16 +9449,16 @@
         <v>387</v>
       </c>
       <c r="AM32" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN32" t="s">
-        <v>420</v>
+        <v>329</v>
       </c>
       <c r="AO32">
-        <v>0.99495603624977191</v>
+        <v>0.99218690980150615</v>
       </c>
       <c r="AP32">
-        <v>92.472668754182365</v>
+        <v>143.23998697238727</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9523,16 +9523,16 @@
         <v>311</v>
       </c>
       <c r="Y33" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="Z33" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="AA33">
-        <v>0.99327889425386662</v>
+        <v>0.96747189690815383</v>
       </c>
       <c r="AB33">
-        <v>123.22027201244609</v>
+        <v>596.34855668384682</v>
       </c>
       <c r="AD33" t="s">
         <v>264</v>
@@ -9562,13 +9562,13 @@
         <v>421</v>
       </c>
       <c r="AN33" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AO33">
-        <v>0.99059324986934494</v>
+        <v>0.98910099910393146</v>
       </c>
       <c r="AP33">
-        <v>172.45708572867548</v>
+        <v>199.81501642792259</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9633,16 +9633,16 @@
         <v>313</v>
       </c>
       <c r="Y34" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Z34" t="s">
         <v>343</v>
       </c>
       <c r="AA34">
-        <v>0.99806574344338672</v>
+        <v>0.99327889425386662</v>
       </c>
       <c r="AB34">
-        <v>35.461370204576532</v>
+        <v>123.22027201244609</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9707,16 +9707,16 @@
         <v>315</v>
       </c>
       <c r="Y35" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Z35" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="AA35">
-        <v>0.99312290929392577</v>
+        <v>0.99022266246501978</v>
       </c>
       <c r="AB35">
-        <v>126.07999627802737</v>
+        <v>179.25118814130403</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9781,16 +9781,16 @@
         <v>317</v>
       </c>
       <c r="Y36" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="Z36" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="AA36">
-        <v>0.96747189690815383</v>
+        <v>0.99592997806909844</v>
       </c>
       <c r="AB36">
-        <v>596.34855668384682</v>
+        <v>74.617068733196106</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9855,16 +9855,16 @@
         <v>319</v>
       </c>
       <c r="Y37" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Z37" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="AA37">
-        <v>0.99117807442989492</v>
+        <v>0.98440782007749728</v>
       </c>
       <c r="AB37">
-        <v>161.73530211859338</v>
+        <v>285.85663191255094</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -9929,16 +9929,16 @@
         <v>321</v>
       </c>
       <c r="Y38" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="Z38" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AA38">
-        <v>0.99199432528561049</v>
+        <v>0.97548412543178475</v>
       </c>
       <c r="AB38">
-        <v>146.77070309714048</v>
+        <v>449.45770041728053</v>
       </c>
     </row>
   </sheetData>
@@ -9947,7 +9947,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F93C25-4E7A-4CD1-8E7C-1EFC50F92AF3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E8AFD7-C631-4093-AFC0-EAFEB56F4AA9}">
   <dimension ref="B9:Z33"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10059,7 +10059,7 @@
         <v>452</v>
       </c>
       <c r="K11" t="s">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="L11">
         <v>2.3509656412756068</v>
@@ -10092,7 +10092,7 @@
         <v>498</v>
       </c>
       <c r="X11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Y11">
         <v>8.3782499999999995</v>
@@ -10127,7 +10127,7 @@
         <v>454</v>
       </c>
       <c r="K12" t="s">
-        <v>416</v>
+        <v>393</v>
       </c>
       <c r="L12">
         <v>8.646252729661045</v>
@@ -10160,7 +10160,7 @@
         <v>500</v>
       </c>
       <c r="X12" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="Y12">
         <v>8.2312499999999993</v>
@@ -10195,7 +10195,7 @@
         <v>456</v>
       </c>
       <c r="K13" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="L13">
         <v>1.5457501567892977</v>
@@ -10228,7 +10228,7 @@
         <v>502</v>
       </c>
       <c r="X13" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="Y13">
         <v>8.9497499999999999</v>
@@ -10263,7 +10263,7 @@
         <v>458</v>
       </c>
       <c r="K14" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="L14">
         <v>25.065653532979095</v>
@@ -10296,7 +10296,7 @@
         <v>504</v>
       </c>
       <c r="X14" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="Y14">
         <v>0.47775000000000001</v>
@@ -10331,7 +10331,7 @@
         <v>460</v>
       </c>
       <c r="K15" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="L15">
         <v>5.9815028333306417</v>
@@ -10364,7 +10364,7 @@
         <v>506</v>
       </c>
       <c r="X15" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Y15">
         <v>0.13425000000000001</v>
@@ -10399,7 +10399,7 @@
         <v>462</v>
       </c>
       <c r="K16" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="L16">
         <v>12.399137262716737</v>
@@ -10432,7 +10432,7 @@
         <v>508</v>
       </c>
       <c r="X16" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="Y16">
         <v>3.92625</v>
@@ -10467,7 +10467,7 @@
         <v>464</v>
       </c>
       <c r="K17" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="L17">
         <v>20.79964040594967</v>
@@ -10500,7 +10500,7 @@
         <v>510</v>
       </c>
       <c r="X17" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="Y17">
         <v>2.2530000000000001</v>
@@ -10535,7 +10535,7 @@
         <v>466</v>
       </c>
       <c r="K18" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="L18">
         <v>9.3777415849931209</v>
@@ -10568,7 +10568,7 @@
         <v>512</v>
       </c>
       <c r="X18" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="Y18">
         <v>6.1852499999999999</v>
@@ -10603,7 +10603,7 @@
         <v>468</v>
       </c>
       <c r="K19" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="L19">
         <v>26.805551801109274</v>
@@ -10636,7 +10636,7 @@
         <v>514</v>
       </c>
       <c r="X19" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="Y19">
         <v>10.093500000000001</v>
@@ -10671,7 +10671,7 @@
         <v>470</v>
       </c>
       <c r="K20" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="L20">
         <v>20.571034962175187</v>
@@ -10704,7 +10704,7 @@
         <v>516</v>
       </c>
       <c r="X20" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="Y20">
         <v>6.7417499999999997</v>
@@ -10739,7 +10739,7 @@
         <v>472</v>
       </c>
       <c r="K21" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="L21">
         <v>15.01601727408983</v>
@@ -10774,7 +10774,7 @@
         <v>474</v>
       </c>
       <c r="K22" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="L22">
         <v>2.3755122289527617</v>
@@ -10809,7 +10809,7 @@
         <v>476</v>
       </c>
       <c r="K23" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="L23">
         <v>15.012351747955419</v>
@@ -10844,7 +10844,7 @@
         <v>478</v>
       </c>
       <c r="K24" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="L24">
         <v>4.3876485804695786</v>
@@ -10879,7 +10879,7 @@
         <v>480</v>
       </c>
       <c r="K25" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="L25">
         <v>6.1536321015103308</v>
@@ -10914,7 +10914,7 @@
         <v>482</v>
       </c>
       <c r="K26" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="L26">
         <v>3.7458169954306517</v>
@@ -10949,7 +10949,7 @@
         <v>484</v>
       </c>
       <c r="K27" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="L27">
         <v>2.899127302163282</v>
@@ -10984,7 +10984,7 @@
         <v>486</v>
       </c>
       <c r="K28" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="L28">
         <v>0.58029073588183855</v>
@@ -11019,7 +11019,7 @@
         <v>488</v>
       </c>
       <c r="K29" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="L29">
         <v>1.000771006718568</v>
@@ -11054,7 +11054,7 @@
         <v>490</v>
       </c>
       <c r="K30" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="L30">
         <v>2.8972001484003882</v>
@@ -11089,7 +11089,7 @@
         <v>492</v>
       </c>
       <c r="K31" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="L31">
         <v>3.577895438171812</v>
@@ -11124,7 +11124,7 @@
         <v>494</v>
       </c>
       <c r="K32" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="L32">
         <v>0.72632903432358276</v>
@@ -11159,7 +11159,7 @@
         <v>496</v>
       </c>
       <c r="K33" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
       <c r="L33">
         <v>1.8165822236221094</v>
@@ -11174,7 +11174,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74CC2662-D4E7-423F-AB42-3FF9FEFD6C34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F278D906-200D-47FB-8264-AE7D01F2E7ED}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
